--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_103_R11.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_103_R11.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.754899999999999</v>
+        <v>9.7446</v>
       </c>
       <c r="E2" t="n">
-        <v>7.7777</v>
+        <v>7.4986</v>
       </c>
       <c r="F2" t="n">
-        <v>1.9772</v>
+        <v>2.2461</v>
       </c>
       <c r="G2" t="n">
         <v>4.2142</v>
@@ -610,13 +610,13 @@
         <v>3.2473</v>
       </c>
       <c r="S2" t="n">
-        <v>1.2212</v>
+        <v>1.2109</v>
       </c>
       <c r="T2" t="n">
-        <v>1.0657</v>
+        <v>0.7866</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1555</v>
+        <v>0.4244</v>
       </c>
       <c r="V2" t="n">
         <v>1.0722</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.3117</v>
+        <v>5.7733</v>
       </c>
       <c r="E3" t="n">
-        <v>3.5235</v>
+        <v>3.2876</v>
       </c>
       <c r="F3" t="n">
-        <v>2.7882</v>
+        <v>2.4857</v>
       </c>
       <c r="G3" t="n">
         <v>4.1119</v>
@@ -688,13 +688,13 @@
         <v>1.8556</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6278</v>
+        <v>0.08939999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9164</v>
+        <v>0.6805</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2886</v>
+        <v>-0.5911</v>
       </c>
       <c r="V3" t="n">
         <v>-0.2836</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.3863</v>
+        <v>3.6297</v>
       </c>
       <c r="E4" t="n">
-        <v>1.0436</v>
+        <v>1.3542</v>
       </c>
       <c r="F4" t="n">
-        <v>2.3427</v>
+        <v>2.2755</v>
       </c>
       <c r="G4" t="n">
         <v>0.354</v>
@@ -766,13 +766,13 @@
         <v>3.2473</v>
       </c>
       <c r="S4" t="n">
-        <v>1.0324</v>
+        <v>1.2757</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3541</v>
+        <v>0.6647</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6783</v>
+        <v>0.6111</v>
       </c>
       <c r="V4" t="n">
         <v>1.0722</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.9363</v>
+        <v>3.4224</v>
       </c>
       <c r="E5" t="n">
-        <v>2.4707</v>
+        <v>2.856</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4656</v>
+        <v>0.5664</v>
       </c>
       <c r="G5" t="n">
         <v>0.4152</v>
@@ -844,13 +844,13 @@
         <v>2.0876</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.3166</v>
+        <v>-0.8305</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.1202</v>
+        <v>-0.735</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1964</v>
+        <v>-0.0955</v>
       </c>
       <c r="V5" t="n">
         <v>1.7501</v>
@@ -877,10 +877,10 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.6782</v>
+        <v>1.2627</v>
       </c>
       <c r="E6" t="n">
-        <v>2.8545</v>
+        <v>1.4391</v>
       </c>
       <c r="F6" t="n">
         <v>-0.1763</v>
@@ -922,10 +922,10 @@
         <v>0.6959</v>
       </c>
       <c r="S6" t="n">
-        <v>1.1914</v>
+        <v>-0.224</v>
       </c>
       <c r="T6" t="n">
-        <v>2.2923</v>
+        <v>0.8768</v>
       </c>
       <c r="U6" t="n">
         <v>-1.1009</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3021</v>
+        <v>0.254</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.5705</v>
+        <v>-1.9808</v>
       </c>
       <c r="F7" t="n">
-        <v>2.2684</v>
+        <v>2.2348</v>
       </c>
       <c r="G7" t="n">
         <v>-2.6119</v>
@@ -1000,13 +1000,13 @@
         <v>2.0876</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0303</v>
+        <v>0.5258</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3576</v>
+        <v>0.2322</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3273</v>
+        <v>0.2937</v>
       </c>
       <c r="V7" t="n">
         <v>0.2525</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.6142</v>
+        <v>-0.4888</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.8882</v>
+        <v>-0.6955</v>
       </c>
       <c r="F8" t="n">
-        <v>0.274</v>
+        <v>0.2068</v>
       </c>
       <c r="G8" t="n">
         <v>-0.0305</v>
@@ -1078,13 +1078,13 @@
         <v>1.1598</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4419</v>
+        <v>-0.3165</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3734</v>
+        <v>-0.1808</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.06850000000000001</v>
+        <v>-0.1357</v>
       </c>
       <c r="V8" t="n">
         <v>-0.1418</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.2828</v>
+        <v>-1.276</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1774</v>
+        <v>0.0161</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.4601</v>
+        <v>-1.2921</v>
       </c>
       <c r="G9" t="n">
         <v>-1.6712</v>
@@ -1156,13 +1156,13 @@
         <v>2.3195</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3009</v>
+        <v>0.3077</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3462</v>
+        <v>0.1849</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0452</v>
+        <v>0.1228</v>
       </c>
       <c r="V9" t="n">
         <v>-1.0722</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>N. HIFI</t>
+          <t>A. M'BAYE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.6073</v>
+        <v>-2.3582</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.0102</v>
+        <v>-0.8381999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>2.4029</v>
+        <v>-1.5201</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.0351</v>
+        <v>-1.9316</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.8752</v>
+        <v>-0.0311</v>
       </c>
       <c r="I10" t="n">
-        <v>1.8401</v>
+        <v>-1.9005</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.7287</v>
+        <v>-1.5243</v>
       </c>
       <c r="K10" t="n">
-        <v>-3.5753</v>
+        <v>-0.4166</v>
       </c>
       <c r="L10" t="n">
-        <v>1.8467</v>
+        <v>-1.1077</v>
       </c>
       <c r="M10" t="n">
-        <v>0.6936</v>
+        <v>-0.4073</v>
       </c>
       <c r="N10" t="n">
-        <v>0.7000999999999999</v>
+        <v>0.3856</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.0065</v>
+        <v>-0.7929</v>
       </c>
       <c r="P10" t="n">
-        <v>-4.4071</v>
+        <v>0.9278</v>
       </c>
       <c r="Q10" t="n">
-        <v>-6.9585</v>
+        <v>-1.1598</v>
       </c>
       <c r="R10" t="n">
-        <v>2.5515</v>
+        <v>2.0876</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3818</v>
+        <v>-1.607</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4604</v>
+        <v>-0.2985</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.8421</v>
+        <v>-1.3084</v>
       </c>
       <c r="V10" t="n">
-        <v>3.2166</v>
+        <v>0.2525</v>
       </c>
       <c r="W10" t="n">
-        <v>3.2166</v>
+        <v>2.1444</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.8919</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. M'BAYE</t>
+          <t>N. HIFI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.0563</v>
+        <v>-2.9873</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.5026</v>
+        <v>-5.2894</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.5537</v>
+        <v>2.3021</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.9316</v>
+        <v>-1.0351</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.0311</v>
+        <v>-2.8752</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.9005</v>
+        <v>1.8401</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.5243</v>
+        <v>-1.7287</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.4166</v>
+        <v>-3.5753</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.1077</v>
+        <v>1.8467</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.4073</v>
+        <v>0.6936</v>
       </c>
       <c r="N11" t="n">
-        <v>0.3856</v>
+        <v>0.7000999999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.7929</v>
+        <v>-0.0065</v>
       </c>
       <c r="P11" t="n">
-        <v>0.9278</v>
+        <v>-4.4071</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1598</v>
+        <v>-6.9585</v>
       </c>
       <c r="R11" t="n">
-        <v>2.0876</v>
+        <v>2.5515</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.305</v>
+        <v>-0.7617</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.963</v>
+        <v>0.1812</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.3421</v>
+        <v>-0.9429</v>
       </c>
       <c r="V11" t="n">
-        <v>0.2525</v>
+        <v>3.2166</v>
       </c>
       <c r="W11" t="n">
-        <v>2.1444</v>
+        <v>3.2166</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.8919</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.8318</v>
+        <v>-3.4204</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.7793</v>
+        <v>-3.4687</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.0526</v>
+        <v>0.0483</v>
       </c>
       <c r="G12" t="n">
         <v>-0.2162</v>
@@ -1390,13 +1390,13 @@
         <v>2.5515</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.4739</v>
+        <v>-1.0624</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1766</v>
+        <v>0.134</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.2972</v>
+        <v>-1.1964</v>
       </c>
       <c r="V12" t="n">
         <v>-1.214</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-9.718500000000001</v>
+        <v>-9.1549</v>
       </c>
       <c r="E13" t="n">
-        <v>-8.270799999999999</v>
+        <v>-7.6063</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.4477</v>
+        <v>-1.5486</v>
       </c>
       <c r="G13" t="n">
         <v>-5.8007</v>
@@ -1468,13 +1468,13 @@
         <v>2.7834</v>
       </c>
       <c r="S13" t="n">
-        <v>0.08210000000000001</v>
+        <v>0.6458</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3576</v>
+        <v>0.3068</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4397</v>
+        <v>0.3389</v>
       </c>
       <c r="V13" t="n">
         <v>-2.1444</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.654400000000003</v>
+        <v>4.401099999999998</v>
       </c>
       <c r="E14" t="n">
-        <v>-4.174200000000001</v>
+        <v>-3.427300000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>7.828600000000001</v>
+        <v>7.828599999999998</v>
       </c>
       <c r="G14" t="n">
         <v>-3.411</v>
@@ -1525,7 +1525,7 @@
         <v>1.7567</v>
       </c>
       <c r="L14" t="n">
-        <v>3.997</v>
+        <v>3.996999999999999</v>
       </c>
       <c r="M14" t="n">
         <v>-9.1647</v>
@@ -1543,16 +1543,16 @@
         <v>-20.8757</v>
       </c>
       <c r="R14" t="n">
-        <v>26.6746</v>
+        <v>26.67460000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.4937</v>
+        <v>-0.7468</v>
       </c>
       <c r="T14" t="n">
-        <v>2.0867</v>
+        <v>2.8334</v>
       </c>
       <c r="U14" t="n">
-        <v>-3.5802</v>
+        <v>-3.58</v>
       </c>
       <c r="V14" t="n">
         <v>2.7601</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. THOMPSON</t>
+          <t>J. PUERTO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.4779</v>
+        <v>3.7146</v>
       </c>
       <c r="E15" t="n">
-        <v>2.7658</v>
+        <v>2.7513</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7121</v>
+        <v>0.9631999999999999</v>
       </c>
       <c r="G15" t="n">
-        <v>1.6011</v>
+        <v>2.9586</v>
       </c>
       <c r="H15" t="n">
-        <v>0.293</v>
+        <v>-0.6985</v>
       </c>
       <c r="I15" t="n">
-        <v>1.3081</v>
+        <v>3.6571</v>
       </c>
       <c r="J15" t="n">
-        <v>2.7126</v>
+        <v>3.4912</v>
       </c>
       <c r="K15" t="n">
-        <v>0.5581</v>
+        <v>-0.4334</v>
       </c>
       <c r="L15" t="n">
-        <v>2.1545</v>
+        <v>3.9247</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.1115</v>
+        <v>-0.5326</v>
       </c>
       <c r="N15" t="n">
         <v>-0.2651</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.8464</v>
+        <v>-0.2676</v>
       </c>
       <c r="P15" t="n">
-        <v>0.9278</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R15" t="n">
-        <v>2.0876</v>
+        <v>1.8556</v>
       </c>
       <c r="S15" t="n">
-        <v>0.271</v>
+        <v>-0.2467</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5351</v>
+        <v>0.5074</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.264</v>
+        <v>-0.7541</v>
       </c>
       <c r="V15" t="n">
-        <v>0.6778999999999999</v>
+        <v>1.4665</v>
       </c>
       <c r="W15" t="n">
-        <v>0.6778999999999999</v>
+        <v>1.0722</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>0.3943</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. PUERTO</t>
+          <t>O. MOORE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.8617</v>
+        <v>3.3711</v>
       </c>
       <c r="E16" t="n">
-        <v>2.5154</v>
+        <v>1.5196</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3462</v>
+        <v>1.8515</v>
       </c>
       <c r="G16" t="n">
-        <v>2.9586</v>
+        <v>0.8847</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.6985</v>
+        <v>0.0181</v>
       </c>
       <c r="I16" t="n">
-        <v>3.6571</v>
+        <v>0.8666</v>
       </c>
       <c r="J16" t="n">
-        <v>3.4912</v>
+        <v>0.924</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.4334</v>
+        <v>0.1043</v>
       </c>
       <c r="L16" t="n">
-        <v>3.9247</v>
+        <v>0.8196</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.5326</v>
+        <v>-0.0393</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.2651</v>
+        <v>-0.0862</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.2676</v>
+        <v>0.047</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.4639</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>-2.3195</v>
       </c>
       <c r="R16" t="n">
-        <v>1.8556</v>
+        <v>2.3195</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.0996</v>
+        <v>0.342</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2715</v>
+        <v>0.7707000000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.3711</v>
+        <v>-0.4288</v>
       </c>
       <c r="V16" t="n">
-        <v>1.4665</v>
+        <v>2.1444</v>
       </c>
       <c r="W16" t="n">
-        <v>1.0722</v>
+        <v>2.1444</v>
       </c>
       <c r="X16" t="n">
-        <v>0.3943</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Y. SIMA</t>
+          <t>D. THOMPSON</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.0289</v>
+        <v>3.2806</v>
       </c>
       <c r="E17" t="n">
-        <v>2.6098</v>
+        <v>2.176</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.5809</v>
+        <v>1.1046</v>
       </c>
       <c r="G17" t="n">
-        <v>1.0762</v>
+        <v>1.6011</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1417</v>
+        <v>0.293</v>
       </c>
       <c r="I17" t="n">
-        <v>1.218</v>
+        <v>1.3081</v>
       </c>
       <c r="J17" t="n">
-        <v>1.0799</v>
+        <v>2.7126</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.2451</v>
+        <v>0.5581</v>
       </c>
       <c r="L17" t="n">
-        <v>1.325</v>
+        <v>2.1545</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.0037</v>
+        <v>-1.1115</v>
       </c>
       <c r="N17" t="n">
-        <v>0.1034</v>
+        <v>-0.2651</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.107</v>
+        <v>-0.8464</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.6959</v>
+        <v>0.9278</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.3195</v>
+        <v>-1.1598</v>
       </c>
       <c r="R17" t="n">
-        <v>1.6237</v>
+        <v>2.0876</v>
       </c>
       <c r="S17" t="n">
-        <v>3.1151</v>
+        <v>0.0738</v>
       </c>
       <c r="T17" t="n">
-        <v>3.7077</v>
+        <v>-0.0547</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5926</v>
+        <v>0.1285</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.4665</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="W17" t="n">
-        <v>0.1418</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.6083</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>O. MOORE</t>
+          <t>J. MONTERO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.5917</v>
+        <v>0.9787</v>
       </c>
       <c r="E18" t="n">
-        <v>0.458</v>
+        <v>-0.374</v>
       </c>
       <c r="F18" t="n">
-        <v>1.1337</v>
+        <v>1.3527</v>
       </c>
       <c r="G18" t="n">
-        <v>0.8847</v>
+        <v>2.1759</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0181</v>
+        <v>0.3925</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8666</v>
+        <v>1.7833</v>
       </c>
       <c r="J18" t="n">
-        <v>0.924</v>
+        <v>1.218</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1043</v>
+        <v>0.007</v>
       </c>
       <c r="L18" t="n">
-        <v>0.8196</v>
+        <v>1.211</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.0393</v>
+        <v>0.9579</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.0862</v>
+        <v>0.3856</v>
       </c>
       <c r="O18" t="n">
-        <v>0.047</v>
+        <v>0.5723</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>0.4639</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.3195</v>
+        <v>-1.1598</v>
       </c>
       <c r="R18" t="n">
-        <v>2.3195</v>
+        <v>1.6237</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.4374</v>
+        <v>-0.5889</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2908</v>
+        <v>-0.4323</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.1466</v>
+        <v>-0.1566</v>
       </c>
       <c r="V18" t="n">
-        <v>2.1444</v>
+        <v>-1.0722</v>
       </c>
       <c r="W18" t="n">
-        <v>2.1444</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. MONTERO</t>
+          <t>Y. SIMA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.7421</v>
+        <v>0.0295</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.374</v>
+        <v>0.4867</v>
       </c>
       <c r="F19" t="n">
-        <v>1.1162</v>
+        <v>-0.4573</v>
       </c>
       <c r="G19" t="n">
-        <v>2.1759</v>
+        <v>1.0762</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3925</v>
+        <v>-0.1417</v>
       </c>
       <c r="I19" t="n">
-        <v>1.7833</v>
+        <v>1.218</v>
       </c>
       <c r="J19" t="n">
-        <v>1.218</v>
+        <v>1.0799</v>
       </c>
       <c r="K19" t="n">
-        <v>0.007</v>
+        <v>-0.2451</v>
       </c>
       <c r="L19" t="n">
-        <v>1.211</v>
+        <v>1.325</v>
       </c>
       <c r="M19" t="n">
-        <v>0.9579</v>
+        <v>-0.0037</v>
       </c>
       <c r="N19" t="n">
-        <v>0.3856</v>
+        <v>0.1034</v>
       </c>
       <c r="O19" t="n">
-        <v>0.5723</v>
+        <v>-0.107</v>
       </c>
       <c r="P19" t="n">
-        <v>0.4639</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R19" t="n">
         <v>1.6237</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8254</v>
+        <v>1.1156</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4323</v>
+        <v>1.5845</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3932</v>
+        <v>-0.4689</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.0722</v>
+        <v>-1.4665</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.0722</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>K. TAYLOR</t>
+          <t>N. REUVERS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.72</v>
+        <v>0.0227</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.6627</v>
+        <v>0.2384</v>
       </c>
       <c r="F20" t="n">
-        <v>1.9427</v>
+        <v>-0.2157</v>
       </c>
       <c r="G20" t="n">
-        <v>0.9233</v>
+        <v>-1.7573</v>
       </c>
       <c r="H20" t="n">
-        <v>0.5653</v>
+        <v>-0.2952</v>
       </c>
       <c r="I20" t="n">
-        <v>0.358</v>
+        <v>-1.4621</v>
       </c>
       <c r="J20" t="n">
-        <v>1.563</v>
+        <v>-1.7364</v>
       </c>
       <c r="K20" t="n">
-        <v>0.8304</v>
+        <v>-0.7023</v>
       </c>
       <c r="L20" t="n">
-        <v>0.7326</v>
+        <v>-1.0341</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.6397</v>
+        <v>-0.021</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2651</v>
+        <v>0.4071</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.3746</v>
+        <v>-0.4281</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.6959</v>
+        <v>0.6959</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.4793</v>
+        <v>-1.1598</v>
       </c>
       <c r="R20" t="n">
-        <v>2.7834</v>
+        <v>1.8556</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0171</v>
+        <v>-0.1298</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8883</v>
+        <v>-0.2238</v>
       </c>
       <c r="U20" t="n">
-        <v>0.8711</v>
+        <v>0.094</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.9304</v>
+        <v>1.214</v>
       </c>
       <c r="W20" t="n">
-        <v>0.1418</v>
+        <v>3.3584</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.0722</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>N. REUVERS</t>
+          <t>K. TAYLOR</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.8816000000000001</v>
+        <v>-0.0396</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.3513</v>
+        <v>-1.8371</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.5303</v>
+        <v>1.7975</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.7573</v>
+        <v>0.9233</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.2952</v>
+        <v>0.5653</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.4621</v>
+        <v>0.358</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.7364</v>
+        <v>1.563</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.7023</v>
+        <v>0.8304</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.0341</v>
+        <v>0.7326</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.021</v>
+        <v>-0.6397</v>
       </c>
       <c r="N21" t="n">
-        <v>0.4071</v>
+        <v>-0.2651</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.4281</v>
+        <v>-0.3746</v>
       </c>
       <c r="P21" t="n">
-        <v>0.6959</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1598</v>
+        <v>-3.4793</v>
       </c>
       <c r="R21" t="n">
-        <v>1.8556</v>
+        <v>2.7834</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0341</v>
+        <v>0.6633</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8136</v>
+        <v>-0.0626</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2205</v>
+        <v>0.726</v>
       </c>
       <c r="V21" t="n">
-        <v>1.214</v>
+        <v>-0.9304</v>
       </c>
       <c r="W21" t="n">
-        <v>3.3584</v>
+        <v>0.1418</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.1444</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>N. SAKO</t>
+          <t>I. NOGUES</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.1963</v>
+        <v>-1.9805</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.7369</v>
+        <v>-1.7155</v>
       </c>
       <c r="F22" t="n">
-        <v>0.5406</v>
+        <v>-0.265</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.7633</v>
+        <v>-0.3252</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.5726</v>
+        <v>-0.4658</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1907</v>
+        <v>0.1406</v>
       </c>
       <c r="J22" t="n">
-        <v>0.3628</v>
+        <v>-0.7327</v>
       </c>
       <c r="K22" t="n">
-        <v>0.2892</v>
+        <v>-0.7695</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0736</v>
+        <v>0.0368</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.1261</v>
+        <v>0.4075</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.8618</v>
+        <v>0.3038</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.2643</v>
+        <v>0.1038</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.4639</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q22" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R22" t="n">
-        <v>0.6959</v>
+        <v>0.232</v>
       </c>
       <c r="S22" t="n">
-        <v>1.4664</v>
+        <v>0.4865</v>
       </c>
       <c r="T22" t="n">
-        <v>0.4955</v>
+        <v>0.177</v>
       </c>
       <c r="U22" t="n">
-        <v>0.9709</v>
+        <v>0.3095</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.4355</v>
+        <v>-1.214</v>
       </c>
       <c r="W22" t="n">
-        <v>-1.4355</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>I. NOGUES</t>
+          <t>N. SAKO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.5765</v>
+        <v>-2.0042</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.4795</v>
+        <v>-2.2087</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.097</v>
+        <v>0.2045</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.3252</v>
+        <v>-0.7633</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.4658</v>
+        <v>-0.5726</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1406</v>
+        <v>-0.1907</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.7327</v>
+        <v>0.3628</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.7695</v>
+        <v>0.2892</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0368</v>
+        <v>0.0736</v>
       </c>
       <c r="M23" t="n">
-        <v>0.4075</v>
+        <v>-1.1261</v>
       </c>
       <c r="N23" t="n">
-        <v>0.3038</v>
+        <v>-0.8618</v>
       </c>
       <c r="O23" t="n">
-        <v>0.1038</v>
+        <v>-0.2643</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.9278</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q23" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R23" t="n">
-        <v>0.232</v>
+        <v>0.6959</v>
       </c>
       <c r="S23" t="n">
-        <v>0.8905</v>
+        <v>0.6585</v>
       </c>
       <c r="T23" t="n">
-        <v>0.4129</v>
+        <v>0.0237</v>
       </c>
       <c r="U23" t="n">
-        <v>0.4775</v>
+        <v>0.6348</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.214</v>
+        <v>-1.4355</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>-1.4355</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.214</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.9434</v>
+        <v>-2.7069</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.8566</v>
+        <v>-3.8003</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9133</v>
+        <v>1.0934</v>
       </c>
       <c r="G24" t="n">
         <v>-1.7173</v>
@@ -2326,13 +2326,13 @@
         <v>2.5515</v>
       </c>
       <c r="S24" t="n">
-        <v>1.7739</v>
+        <v>1.0104</v>
       </c>
       <c r="T24" t="n">
-        <v>1.3214</v>
+        <v>0.3778</v>
       </c>
       <c r="U24" t="n">
-        <v>0.4525</v>
+        <v>0.6326000000000001</v>
       </c>
       <c r="V24" t="n">
         <v>-1.0722</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.9877</v>
+        <v>-2.8761</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.0637</v>
+        <v>-2.1201</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.924</v>
+        <v>-0.756</v>
       </c>
       <c r="G25" t="n">
         <v>-1.6309</v>
@@ -2404,13 +2404,13 @@
         <v>1.6237</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.5012</v>
+        <v>0.6104000000000001</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.4481</v>
+        <v>0.4955</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.0532</v>
+        <v>0.1149</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-4.051</v>
+        <v>-3.0852</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.6527</v>
+        <v>-2.945</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.3983</v>
+        <v>-0.1402</v>
       </c>
       <c r="G26" t="n">
         <v>-0.0149</v>
@@ -2482,13 +2482,13 @@
         <v>1.6237</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.1084</v>
+        <v>-0.1426</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.2908</v>
+        <v>0.4169</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.8175</v>
+        <v>-0.5594</v>
       </c>
       <c r="V26" t="n">
         <v>-1.0722</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-3.654199999999999</v>
+        <v>-1.2953</v>
       </c>
       <c r="E27" t="n">
-        <v>-7.8284</v>
+        <v>-7.8287</v>
       </c>
       <c r="F27" t="n">
-        <v>4.174300000000001</v>
+        <v>6.533200000000001</v>
       </c>
       <c r="G27" t="n">
         <v>3.4109</v>
@@ -2530,7 +2530,7 @@
         <v>-3.4149</v>
       </c>
       <c r="I27" t="n">
-        <v>6.8258</v>
+        <v>6.825800000000001</v>
       </c>
       <c r="J27" t="n">
         <v>9.1647</v>
@@ -2560,13 +2560,13 @@
         <v>20.8759</v>
       </c>
       <c r="S27" t="n">
-        <v>1.4937</v>
+        <v>3.8525</v>
       </c>
       <c r="T27" t="n">
-        <v>3.5802</v>
+        <v>3.5801</v>
       </c>
       <c r="U27" t="n">
-        <v>-2.0867</v>
+        <v>0.2724999999999999</v>
       </c>
       <c r="V27" t="n">
         <v>-2.7602</v>
@@ -2575,7 +2575,7 @@
         <v>6.101</v>
       </c>
       <c r="X27" t="n">
-        <v>-8.861200000000002</v>
+        <v>-8.8612</v>
       </c>
     </row>
   </sheetData>
